--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:16</t>
+    <t xml:space="preserve">2026-09-09 22:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:15</t>
+    <t xml:space="preserve">2026-09-17 13:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,18 +955,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>11.11</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>11.41</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="4">
@@ -1015,68 +1015,68 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>12.27</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11.11</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>12.09</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11.56</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11.41</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="8">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:41</t>
+    <t xml:space="preserve">2026-09-25 21:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -527,10 +527,10 @@
         <v>12.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.69</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-5.39</v>
+        <v>-5.35</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>5</v>
@@ -573,10 +573,10 @@
         <v>10.33</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3.68</v>
+        <v>-3.61</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -622,7 +622,7 @@
         <v>-0.82</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-8.49</v>
+        <v>-8.48</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>-0.51</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4.39</v>
+        <v>-4.36</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>
@@ -668,7 +668,7 @@
         <v>0.43</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -688,10 +688,10 @@
         <v>9.7</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-6.08</v>
+        <v>-6.17</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3</v>
@@ -711,10 +711,10 @@
         <v>11.56</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1.35</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
         <v>-0.12</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.82</v>
+        <v>-0.8</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
@@ -760,7 +760,7 @@
         <v>-0.89</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-8.93</v>
+        <v>-8.96</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -783,7 +783,7 @@
         <v>-0.56</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4.64</v>
+        <v>-4.65</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -806,7 +806,7 @@
         <v>-1.17</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-6.84</v>
+        <v>-6.86</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
@@ -826,10 +826,10 @@
         <v>10.81</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-1.55</v>
+        <v>-1.56</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-14.34</v>
+        <v>-14.39</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -849,10 +849,10 @@
         <v>13.49</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-1.39</v>
+        <v>-1.4</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-10.3</v>
+        <v>-10.35</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_los_lagos.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:40</t>
+    <t xml:space="preserve">2026-10-05 07:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
